--- a/tests/testthat/golden/demo/demo_desctab.xlsx
+++ b/tests/testthat/golden/demo/demo_desctab.xlsx
@@ -15,13 +15,14 @@
     <sheet name="Small Cells Primary" sheetId="7" r:id="rId9"/>
     <sheet name="Small Cells Complement" sheetId="8" r:id="rId10"/>
     <sheet name="Small Cells Binary" sheetId="9" r:id="rId11"/>
+    <sheet name="Small Cells Primary Mode" sheetId="10" r:id="rId12"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="325" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="362" uniqueCount="90">
   <si>
     <t>Repair record distribution</t>
   </si>
@@ -270,13 +271,34 @@
   </si>
   <si>
     <t>N=100</t>
+  </si>
+  <si>
+    <t>Small-cell suppression: primary mode</t>
+  </si>
+  <si>
+    <t>8 (80)</t>
+  </si>
+  <si>
+    <t>6 (60)</t>
+  </si>
+  <si>
+    <t>8 (40)</t>
+  </si>
+  <si>
+    <t>12 (60)</t>
+  </si>
+  <si>
+    <t>0.068</t>
+  </si>
+  <si>
+    <t>Counts from 1 to 4 are shown as &lt;5 without a percentage (primary suppression only: no complementary cells are masked, and other cells, totals and tests are shown as computed). This protects printed counts only.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="8">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -286,32 +308,23 @@
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="12"/>
+      <b/>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
       <sz val="12"/>
       <name val="Arial"/>
-      <b/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
       <b/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <b/>
+      <sz val="12"/>
       <name val="Arial"/>
     </font>
     <font>
+      <i/>
       <sz val="8"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Arial"/>
-      <i/>
     </font>
   </fonts>
   <fills count="5">
@@ -323,21 +336,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDBE5F1"/>
+        <fgColor rgb="FFEDF2F9"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEDF2F9"/>
+        <fgColor rgb="FFDBE5F1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEBCD"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="18">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -347,371 +363,273 @@
     </border>
     <border/>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="none"/>
-      <top style="none"/>
+      <right style="thin"/>
+      <top/>
       <bottom style="thin"/>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
+      <left/>
       <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
+      <left/>
       <right style="thin"/>
-      <top style="none"/>
+      <top/>
       <bottom style="thin"/>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
+      <left/>
       <right style="thin"/>
       <top style="thin"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="thin"/>
-      <top style="none"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left/>
+      <right/>
       <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="none"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin"/>
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="thin"/>
+      <left/>
+      <right/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal style="none"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="general" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="bottom" wrapText="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -731,13 +649,13 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -745,10 +663,10 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="11" t="s">
         <v>9</v>
       </c>
     </row>
@@ -756,10 +674,10 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="26" t="s">
+      <c r="B3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>10</v>
       </c>
     </row>
@@ -767,10 +685,10 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="8" t="s">
         <v>1</v>
       </c>
     </row>
@@ -778,10 +696,10 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="31" t="s">
+      <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
     </row>
@@ -789,10 +707,10 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -800,10 +718,10 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="6" t="s">
         <v>13</v>
       </c>
     </row>
@@ -811,10 +729,10 @@
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -822,10 +740,10 @@
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="32" t="s">
+      <c r="C9" s="7" t="s">
         <v>15</v>
       </c>
     </row>
@@ -833,6 +751,158 @@
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="B2:B3"/>
+  </mergeCells>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
+    <col min="2" max="2" width="15.7109375" style="1" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" style="1" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" style="1" customWidth="true"/>
+    <col min="5" max="5" width="12.7109375" style="1" customWidth="true"/>
+    <col min="6" max="6" width="10.7109375" style="1" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="57" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="57" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="56" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" s="55" t="s">
+        <v>69</v>
+      </c>
+      <c r="E2" s="56" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="56" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="E3" s="54" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" s="54" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="51" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="52" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="52" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="47" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="48" t="s">
+        <v>86</v>
+      </c>
+      <c r="F5" s="48" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="45" t="s">
+        <v>65</v>
+      </c>
+      <c r="C6" s="49" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="E6" s="50" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="50" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="0"/>
+      <c r="D7" s="0"/>
+      <c r="E7" s="0"/>
+      <c r="F7" s="0"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="B7:F7"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -848,13 +918,13 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -862,10 +932,10 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="21" t="s">
         <v>9</v>
       </c>
     </row>
@@ -873,10 +943,10 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="36" t="s">
+      <c r="B3" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>10</v>
       </c>
     </row>
@@ -884,10 +954,10 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="8" t="s">
         <v>1</v>
       </c>
     </row>
@@ -895,10 +965,10 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="37" t="s">
+      <c r="B5" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="38" t="s">
+      <c r="C5" s="17" t="s">
         <v>11</v>
       </c>
     </row>
@@ -906,10 +976,10 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="31" t="s">
+      <c r="C6" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -917,10 +987,10 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="C7" s="17" t="s">
         <v>13</v>
       </c>
     </row>
@@ -928,10 +998,10 @@
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="6" t="s">
         <v>14</v>
       </c>
     </row>
@@ -939,10 +1009,10 @@
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="39" t="s">
+      <c r="B9" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="40" t="s">
+      <c r="C9" s="18" t="s">
         <v>15</v>
       </c>
     </row>
@@ -967,19 +1037,19 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -987,16 +1057,16 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="12" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1004,16 +1074,16 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="10" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1021,16 +1091,16 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="E4" s="26" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1038,16 +1108,16 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="43" t="s">
+      <c r="C5" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="43" t="s">
+      <c r="D5" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="24" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1073,19 +1143,19 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1093,16 +1163,16 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="12" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1110,16 +1180,16 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="10" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1127,16 +1197,16 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="47" t="s">
+      <c r="B4" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="49" t="s">
+      <c r="C4" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="49" t="s">
+      <c r="D4" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="50" t="s">
+      <c r="E4" s="31" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1162,19 +1232,19 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1182,16 +1252,16 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="12" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1199,16 +1269,16 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="10" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1216,16 +1286,16 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="25" t="s">
         <v>43</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="E4" s="26" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1233,16 +1303,16 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5" s="51" t="s">
+      <c r="C5" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5" s="33" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1250,16 +1320,16 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="E6" s="51" t="s">
+      <c r="E6" s="33" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1267,16 +1337,16 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="51" t="s">
+      <c r="E7" s="33" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1284,16 +1354,16 @@
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="E8" s="51" t="s">
+      <c r="E8" s="33" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1301,16 +1371,16 @@
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="E9" s="51" t="s">
+      <c r="E9" s="33" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1318,16 +1388,16 @@
       <c r="A10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B10" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="43" t="s">
+      <c r="C10" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="43" t="s">
+      <c r="D10" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="E10" s="24" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1355,25 +1425,25 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="G1" s="3" t="s">
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1381,22 +1451,22 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="F2" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="12" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1404,22 +1474,22 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="21" t="s">
+      <c r="E3" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="39" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="10" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1427,22 +1497,22 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="52" t="s">
+      <c r="E4" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="F4" s="52" t="s">
+      <c r="F4" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="56" t="s">
+      <c r="G4" s="38" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1450,22 +1520,22 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="53" t="s">
+      <c r="E5" s="34" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="53" t="s">
+      <c r="F5" s="34" t="s">
         <v>57</v>
       </c>
-      <c r="G5" s="58" t="s">
+      <c r="G5" s="37" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1473,22 +1543,22 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="23" t="s">
+      <c r="B6" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6" s="53" t="s">
+      <c r="C6" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6" s="34" t="s">
         <v>56</v>
       </c>
-      <c r="F6" s="53" t="s">
+      <c r="F6" s="34" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="58" t="s">
+      <c r="G6" s="37" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1496,22 +1566,22 @@
       <c r="A7" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" s="51" t="s">
+      <c r="E7" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F7" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="33" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1519,22 +1589,22 @@
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="32" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" s="51" t="s">
+      <c r="E8" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="33" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1542,22 +1612,22 @@
       <c r="A9" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="32" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="32" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="F9" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" s="51" t="s">
+      <c r="E9" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="33" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1565,22 +1635,22 @@
       <c r="A10" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="32" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="53" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" s="51" t="s">
+      <c r="E10" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" s="33" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1588,22 +1658,22 @@
       <c r="A11" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="43" t="s">
+      <c r="C11" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="D11" s="43" t="s">
+      <c r="D11" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="F11" s="54" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" s="44" t="s">
+      <c r="E11" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="24" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1632,22 +1702,22 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1655,19 +1725,19 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="12" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1675,19 +1745,19 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="27" t="s">
         <v>67</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="10" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1695,19 +1765,19 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="42" t="s">
+      <c r="C4" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="26" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1715,19 +1785,19 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="51" t="s">
+      <c r="E5" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="F5" s="51" t="s">
+      <c r="F5" s="33" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1735,24 +1805,24 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="E6" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="F6" s="24" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="63" t="s">
+      <c r="B7" s="41" t="s">
         <v>73</v>
       </c>
       <c r="C7" s="0"/>
@@ -1784,22 +1854,22 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1807,19 +1877,19 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="12" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1827,19 +1897,19 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="27" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="10" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1847,19 +1917,19 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="42" t="s">
+      <c r="C4" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="26" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1867,19 +1937,19 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="E5" s="51" t="s">
+      <c r="E5" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="F5" s="51" t="s">
+      <c r="F5" s="33" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1887,24 +1957,24 @@
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="24" t="s">
+      <c r="B6" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C6" s="43" t="s">
+      <c r="C6" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="23" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="44" t="s">
+      <c r="E6" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="F6" s="24" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="63" t="s">
+      <c r="B7" s="41" t="s">
         <v>73</v>
       </c>
       <c r="C7" s="0"/>
@@ -1936,22 +2006,22 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="3" t="s">
+      <c r="B1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1959,19 +2029,19 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="12" t="s">
         <v>28</v>
       </c>
     </row>
@@ -1979,19 +2049,19 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="27" t="s">
         <v>81</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="10" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1999,24 +2069,24 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="47" t="s">
+      <c r="B4" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="49" t="s">
+      <c r="C4" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="49" t="s">
+      <c r="D4" s="30" t="s">
         <v>68</v>
       </c>
-      <c r="E4" s="50" t="s">
+      <c r="E4" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="50" t="s">
+      <c r="F4" s="31" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="63" t="s">
+      <c r="B5" s="41" t="s">
         <v>73</v>
       </c>
       <c r="C5" s="0"/>
